--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>울산pt핏버디짐</t>
+          <t>헌트피트니스 옥동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fitbuddy@naver.com</t>
+          <t>huntfitness_2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1335-5805</t>
+          <t>0507-1422-1553</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 남구 월평로 72</t>
+          <t>울산 남구 동산로29번길 4 2-3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitbuddy</t>
+          <t>https://blog.naver.com/huntfitness_2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wk5k</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>1070</v>
       </c>
       <c r="Q2" t="n">
-        <v>271</v>
+        <v>1929</v>
       </c>
       <c r="R2" t="n">
-        <v>371</v>
+        <v>2999</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1562351903</t>
+          <t>1960233397</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1562351903</t>
+          <t>https://m.place.naver.com/place/1960233397</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헌트피트니스 옥동점</t>
+          <t>에프포짐 헬스장&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>huntfitness_2@naver.com</t>
+          <t>f4fitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1422-1553</t>
+          <t>0507-1415-7783</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>울산 남구 동산로29번길 4 2-3층</t>
+          <t>울산 남구 삼산중로 71 3,4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huntfitness_2</t>
+          <t>https://blog.naver.com/f4fitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcc02l</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1069</v>
+        <v>1083</v>
       </c>
       <c r="Q3" t="n">
-        <v>1924</v>
+        <v>492</v>
       </c>
       <c r="R3" t="n">
-        <v>2993</v>
+        <v>1575</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1960233397</t>
+          <t>33706478</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1960233397</t>
+          <t>https://m.place.naver.com/place/33706478</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에프포짐 헬스장&amp;PT 삼산점</t>
+          <t>울산 PT전문 스페스짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>f4fitness@naver.com</t>
+          <t>spesgym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-7783</t>
+          <t>0507-1441-0978</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 삼산중로 71 3,4층</t>
+          <t>울산 남구 봉월로59번길 10 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f4fitness</t>
+          <t>https://www.instagram.com/spesgym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcc02l</t>
+          <t>https://talk.naver.com/ct/wosoak8</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1082</v>
+        <v>106</v>
       </c>
       <c r="Q4" t="n">
-        <v>491</v>
+        <v>646</v>
       </c>
       <c r="R4" t="n">
-        <v>1573</v>
+        <v>752</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>33706478</t>
+          <t>1311964904</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33706478</t>
+          <t>https://m.place.naver.com/place/1311964904</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>울산 PT전문 스페스짐</t>
+          <t>레코드핏 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spesgym@naver.com</t>
+          <t>record_fit@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1441-0978</t>
+          <t>0507-1464-2312</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>울산 남구 봉월로59번길 10 4층</t>
+          <t>울산 남구 번영로 12 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spesgym</t>
+          <t>https://www.instagram.com/ulsan_recordfit/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wosoak8</t>
+          <t>https://talk.naver.com/ct/wi1tphq</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="Q5" t="n">
-        <v>641</v>
+        <v>420</v>
       </c>
       <c r="R5" t="n">
-        <v>747</v>
+        <v>586</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1311964904</t>
+          <t>1242710358</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311964904</t>
+          <t>https://m.place.naver.com/place/1242710358</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1046,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레코드핏 헬스&amp;PT</t>
+          <t>온앤온피티스튜디오</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>record_fit@naver.com</t>
+          <t>thelastgym2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1464-2312</t>
+          <t>0507-1374-9854</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 번영로 12 5층</t>
+          <t>울산 북구 동대로 142 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ulsan_recordfit/</t>
+          <t>https://www.instagram.com/on_n_on_p.t_studio?igsh=MWtxajZ4Z290cTZucQ==</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi1tphq</t>
+          <t>https://talk.naver.com/ct/w4m9rk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="n">
-        <v>420</v>
+        <v>49</v>
       </c>
       <c r="R7" t="n">
-        <v>586</v>
+        <v>139</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1242710358</t>
+          <t>1467612314</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1242710358</t>
+          <t>https://m.place.naver.com/place/1467612314</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1139,34 +1139,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>온앤온피티스튜디오</t>
+          <t>더브로짐 호계매곡점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>thelastgym2@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1374-9854</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 북구 동대로 142 2층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/on_n_on_p.t_studio?igsh=MWtxajZ4Z290cTZucQ==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4m9rk</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="R8" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1467612314</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467612314</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT야음점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bemoveyaeum@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1386-7929</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bemoveyaeum</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ujg</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2206</v>
+        <v>168</v>
       </c>
       <c r="Q9" t="n">
-        <v>498</v>
+        <v>44</v>
       </c>
       <c r="R9" t="n">
-        <v>2704</v>
+        <v>212</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1092788853</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092788853</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,39 +1335,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
+          <t>https://talk.naver.com/ct/w423pi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1019</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>467</v>
       </c>
       <c r="R10" t="n">
-        <v>12</v>
+        <v>1486</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더브로짐 호계매곡점</t>
+          <t>휘트니스클리닉 울산동구점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>fitnessclinic_ulsan1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1304-6479</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 동구 대학길 30 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,42 +1470,38 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="Q11" t="n">
-        <v>96</v>
+        <v>300</v>
       </c>
       <c r="R11" t="n">
-        <v>156</v>
+        <v>426</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>242237435</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/242237435</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="Q2" t="n">
-        <v>1929</v>
+        <v>1972</v>
       </c>
       <c r="R2" t="n">
-        <v>2999</v>
+        <v>3052</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="Q3" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="R3" t="n">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>울산 PT전문 스페스짐</t>
+          <t>디엔피트니스 PT\u002F헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spesgym@naver.com</t>
+          <t>dnfit@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1441-0978</t>
+          <t>0507-1478-3239</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 봉월로59번길 10 4층</t>
+          <t>울산 남구 번영로 51 3층 디엔피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spesgym</t>
+          <t>https://www.instagram.com/dnfit_official</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -798,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wosoak8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="Q4" t="n">
-        <v>646</v>
+        <v>96</v>
       </c>
       <c r="R4" t="n">
-        <v>752</v>
+        <v>221</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1311964904</t>
+          <t>1215017007</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311964904</t>
+          <t>https://m.place.naver.com/place/1215017007</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -854,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>레코드핏 헬스&amp;PT</t>
+          <t>울산pt핏버디짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>record_fit@naver.com</t>
+          <t>fitbuddy@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1464-2312</t>
+          <t>0507-1335-5805</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>울산 남구 번영로 12 5층</t>
+          <t>울산 남구 월평로 72</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ulsan_recordfit/</t>
+          <t>https://blog.naver.com/fitbuddy</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,12 +897,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi1tphq</t>
+          <t>https://talk.naver.com/ct/w5wk5k</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
-        <v>420</v>
+        <v>262</v>
       </c>
       <c r="R5" t="n">
-        <v>586</v>
+        <v>362</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,52 +926,56 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1242710358</t>
+          <t>1562351903</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1242710358</t>
+          <t>https://m.place.naver.com/place/1562351903</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>바른핏헬스 앤 PT 울산점</t>
+          <t>다이트짐 헬스&amp;PT 울산삼산본점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>allbareun_3822@naver.com</t>
+          <t>ditegym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1446-8926</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 남구 수암로 165 용진빌딩 7층</t>
+          <t>울산 남구 번영로 234 4층 401호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/allbareun_3822</t>
+          <t>https://ditegym.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4oeeq</t>
+          <t>https://talk.naver.com/ct/wkujcar</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>124</v>
+        <v>1383</v>
       </c>
       <c r="Q6" t="n">
-        <v>469</v>
+        <v>1976</v>
       </c>
       <c r="R6" t="n">
-        <v>593</v>
+        <v>3359</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,51 +1024,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1481331103</t>
+          <t>1071156655</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481331103</t>
+          <t>https://m.place.naver.com/place/1071156655</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>온앤온피티스튜디오</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thelastgym2@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1374-9854</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 북구 동대로 142 2층</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/on_n_on_p.t_studio?igsh=MWtxajZ4Z290cTZucQ==</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4m9rk</t>
+          <t>https://talk.naver.com/ct/w40ujg</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>90</v>
+        <v>2227</v>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>508</v>
       </c>
       <c r="R7" t="n">
-        <v>139</v>
+        <v>2735</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1467612314</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467612314</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1144,39 +1144,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더브로짐 호계매곡점</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,18 +1299,18 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>105</v>
+      </c>
+      <c r="R9" t="n">
         <v>168</v>
       </c>
-      <c r="Q9" t="n">
-        <v>44</v>
-      </c>
-      <c r="R9" t="n">
-        <v>212</v>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1019</v>
+        <v>176</v>
       </c>
       <c r="Q10" t="n">
-        <v>467</v>
+        <v>53</v>
       </c>
       <c r="R10" t="n">
-        <v>1486</v>
+        <v>229</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1438,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스클리닉 울산동구점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fitnessclinic_ulsan1@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1304-6479</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 동구 대학길 30 지하1층</t>
+          <t>울산 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,13 +1480,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w423pi</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>126</v>
+        <v>1028</v>
       </c>
       <c r="Q11" t="n">
-        <v>300</v>
+        <v>463</v>
       </c>
       <c r="R11" t="n">
-        <v>426</v>
+        <v>1491</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,17 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>242237435</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/242237435</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헌트피트니스 옥동점</t>
+          <t>고다필라테스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>huntfitness_2@naver.com</t>
+          <t>godapilates@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1422-1553</t>
+          <t>0507-1436-5650</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 남구 동산로29번길 4 2-3층</t>
+          <t>울산 남구 대암로 109 4층 고다필라테스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huntfitness_2</t>
+          <t>https://www.instagram.com/goda_pilates</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1080</v>
+        <v>472</v>
       </c>
       <c r="Q2" t="n">
-        <v>1972</v>
+        <v>153</v>
       </c>
       <c r="R2" t="n">
-        <v>3052</v>
+        <v>625</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1960233397</t>
+          <t>1488235766</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1960233397</t>
+          <t>https://m.place.naver.com/place/1488235766</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에프포짐 헬스장&amp;PT 삼산점</t>
+          <t>헌트피트니스 옥동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>f4fitness@naver.com</t>
+          <t>huntfitness_2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1415-7783</t>
+          <t>0507-1422-1553</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>울산 남구 삼산중로 71 3,4층</t>
+          <t>울산 남구 동산로29번길 4 2-3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f4fitness</t>
+          <t>https://blog.naver.com/huntfitness_2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcc02l</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="Q3" t="n">
-        <v>495</v>
+        <v>1978</v>
       </c>
       <c r="R3" t="n">
-        <v>1585</v>
+        <v>3062</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>33706478</t>
+          <t>1960233397</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33706478</t>
+          <t>https://m.place.naver.com/place/1960233397</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디엔피트니스 PT\u002F헬스</t>
+          <t>에프포짐 헬스장&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dnfit@naver.com</t>
+          <t>f4fitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1478-3239</t>
+          <t>0507-1415-7783</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 번영로 51 3층 디엔피트니스</t>
+          <t>울산 남구 삼산중로 71 3,4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dnfit_official</t>
+          <t>https://blog.naver.com/f4fitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,15 +789,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcc02l</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>125</v>
+        <v>1094</v>
       </c>
       <c r="Q4" t="n">
-        <v>96</v>
+        <v>495</v>
       </c>
       <c r="R4" t="n">
-        <v>221</v>
+        <v>1589</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1215017007</t>
+          <t>33706478</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215017007</t>
+          <t>https://m.place.naver.com/place/33706478</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -936,41 +936,41 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이트짐 헬스&amp;PT 울산삼산본점</t>
+          <t>디엔피트니스 PT\u002F헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ditegym@naver.com</t>
+          <t>dnfit@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1446-8926</t>
+          <t>0507-1478-3239</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 남구 번영로 234 4층 401호</t>
+          <t>울산 남구 번영로 51 3층 디엔피트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://ditegym.com/</t>
+          <t>https://www.instagram.com/dnfit_official</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -990,17 +990,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkujcar</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1383</v>
+        <v>127</v>
       </c>
       <c r="Q6" t="n">
-        <v>1976</v>
+        <v>96</v>
       </c>
       <c r="R6" t="n">
-        <v>3359</v>
+        <v>223</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,51 +1020,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1071156655</t>
+          <t>1215017007</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071156655</t>
+          <t>https://m.place.naver.com/place/1215017007</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT야음점</t>
+          <t>울산 PT전문 스페스짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bemoveyaeum@naver.com</t>
+          <t>spesgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1386-7929</t>
+          <t>0507-1441-0978</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
+          <t>울산 남구 봉월로59번길 10 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bemoveyaeum</t>
+          <t>https://www.instagram.com/spesgym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1079,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1089,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ujg</t>
+          <t>https://talk.naver.com/ct/wosoak8</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2227</v>
+        <v>106</v>
       </c>
       <c r="Q7" t="n">
-        <v>508</v>
+        <v>695</v>
       </c>
       <c r="R7" t="n">
-        <v>2735</v>
+        <v>801</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,51 +1118,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1092788853</t>
+          <t>1311964904</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092788853</t>
+          <t>https://m.place.naver.com/place/1311964904</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>온앤온피티스튜디오</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>thelastgym2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1374-9854</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 북구 동대로 142 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https://www.instagram.com/on_n_on_p.t_studio?igsh=MWtxajZ4Z290cTZucQ==</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,7 +1177,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
+          <t>https://talk.naver.com/ct/w4m9rk</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="R8" t="n">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>1467612314</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/1467612314</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,12 +1270,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w40ujg</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,17 +1295,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>63</v>
+        <v>2228</v>
       </c>
       <c r="Q9" t="n">
-        <v>105</v>
+        <v>508</v>
       </c>
       <c r="R9" t="n">
-        <v>168</v>
+        <v>2736</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1314,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1340,34 +1336,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1377,7 +1373,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>176</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>229</v>
+        <v>31</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1412,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1438,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,12 +1466,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,17 +1491,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1028</v>
+        <v>63</v>
       </c>
       <c r="Q11" t="n">
-        <v>463</v>
+        <v>105</v>
       </c>
       <c r="R11" t="n">
-        <v>1491</v>
+        <v>168</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1510,115 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fitpointgym24@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1369-1554</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitpointgym24</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>54</v>
+      </c>
+      <c r="R12" t="n">
+        <v>235</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2023664509</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2023664509</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>고다필라테스</t>
+          <t>헌트피트니스 옥동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>godapilates@naver.com</t>
+          <t>huntfitness_2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1436-5650</t>
+          <t>0507-1422-1553</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 남구 대암로 109 4층 고다필라테스</t>
+          <t>울산 남구 동산로29번길 4 2-3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goda_pilates</t>
+          <t>https://blog.naver.com/huntfitness_2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>472</v>
+        <v>1084</v>
       </c>
       <c r="Q2" t="n">
-        <v>153</v>
+        <v>1977</v>
       </c>
       <c r="R2" t="n">
-        <v>625</v>
+        <v>3061</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1488235766</t>
+          <t>1960233397</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488235766</t>
+          <t>https://m.place.naver.com/place/1960233397</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헌트피트니스 옥동점</t>
+          <t>에프포짐 헬스장&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>huntfitness_2@naver.com</t>
+          <t>f4fitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1422-1553</t>
+          <t>0507-1415-7783</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>울산 남구 동산로29번길 4 2-3층</t>
+          <t>울산 남구 삼산중로 71 3,4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huntfitness_2</t>
+          <t>https://blog.naver.com/f4fitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcc02l</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="Q3" t="n">
-        <v>1978</v>
+        <v>495</v>
       </c>
       <c r="R3" t="n">
-        <v>3062</v>
+        <v>1589</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1960233397</t>
+          <t>33706478</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1960233397</t>
+          <t>https://m.place.naver.com/place/33706478</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에프포짐 헬스장&amp;PT 삼산점</t>
+          <t>디엔피트니스 PT\u002F헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>f4fitness@naver.com</t>
+          <t>dnfit@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-7783</t>
+          <t>0507-1478-3239</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 삼산중로 71 3,4층</t>
+          <t>울산 남구 번영로 51 3층 디엔피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f4fitness</t>
+          <t>https://www.instagram.com/dnfit_official</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,19 +793,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcc02l</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1094</v>
+        <v>127</v>
       </c>
       <c r="Q4" t="n">
-        <v>495</v>
+        <v>96</v>
       </c>
       <c r="R4" t="n">
-        <v>1589</v>
+        <v>223</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>33706478</t>
+          <t>1215017007</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33706478</t>
+          <t>https://m.place.naver.com/place/1215017007</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -948,34 +948,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>디엔피트니스 PT\u002F헬스</t>
+          <t>울산 PT전문 스페스짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dnfit@naver.com</t>
+          <t>spesgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1478-3239</t>
+          <t>0507-1441-0978</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 남구 번영로 51 3층 디엔피트니스</t>
+          <t>울산 남구 봉월로59번길 10 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dnfit_official</t>
+          <t>https://www.instagram.com/spesgym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -985,15 +985,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wosoak8</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1005,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="Q6" t="n">
-        <v>96</v>
+        <v>699</v>
       </c>
       <c r="R6" t="n">
-        <v>223</v>
+        <v>805</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1215017007</t>
+          <t>1311964904</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215017007</t>
+          <t>https://m.place.naver.com/place/1311964904</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1037,34 +1041,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>울산 PT전문 스페스짐</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>spesgym@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1441-0978</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 봉월로59번길 10 4층</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spesgym</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1079,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1089,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wosoak8</t>
+          <t>https://talk.naver.com/ct/w40ujg</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1103,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>106</v>
+        <v>2228</v>
       </c>
       <c r="Q7" t="n">
-        <v>695</v>
+        <v>508</v>
       </c>
       <c r="R7" t="n">
-        <v>801</v>
+        <v>2736</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1311964904</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311964904</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1135,34 +1139,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>온앤온피티스튜디오</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>thelastgym2@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1374-9854</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 북구 동대로 142 2층</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/on_n_on_p.t_studio?igsh=MWtxajZ4Z290cTZucQ==</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,7 +1181,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1187,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4m9rk</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="R8" t="n">
-        <v>139</v>
+        <v>32</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1467612314</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467612314</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT야음점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bemoveyaeum@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1386-7929</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bemoveyaeum</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,12 +1274,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ujg</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1295,17 +1299,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2228</v>
+        <v>63</v>
       </c>
       <c r="Q9" t="n">
-        <v>508</v>
+        <v>105</v>
       </c>
       <c r="R9" t="n">
-        <v>2736</v>
+        <v>168</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1092788853</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092788853</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,34 +1340,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1373,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>181</v>
       </c>
       <c r="Q10" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="R10" t="n">
-        <v>31</v>
+        <v>235</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1466,12 +1470,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1481,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w423pi</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1491,17 +1495,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>63</v>
+        <v>1031</v>
       </c>
       <c r="Q11" t="n">
-        <v>105</v>
+        <v>459</v>
       </c>
       <c r="R11" t="n">
-        <v>168</v>
+        <v>1490</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,113 +1514,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>fitpointgym24@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1369-1554</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>181</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>54</v>
-      </c>
-      <c r="R12" t="n">
-        <v>235</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2023664509</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헌트피트니스 옥동점</t>
+          <t>박터짐24 헬스&amp;PT 울주군 덕신점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>huntfitness_2@naver.com</t>
+          <t>baktergym1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1422-1553</t>
+          <t>0507-1439-5893</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 남구 동산로29번길 4 2-3층</t>
+          <t>울산광역시 울주군 온산읍 신경5길 36 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huntfitness_2</t>
+          <t>https://www.instagram.com/baktergym24_ducksin?igsh=MTd6NmcxeWw2ejNsNw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1084</v>
+        <v>527</v>
       </c>
       <c r="Q2" t="n">
-        <v>1977</v>
+        <v>172</v>
       </c>
       <c r="R2" t="n">
-        <v>3061</v>
+        <v>699</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1960233397</t>
+          <t>1682330733</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1960233397</t>
+          <t>https://m.place.naver.com/place/1682330733</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에프포짐 헬스장&amp;PT 삼산점</t>
+          <t>헌트피트니스 옥동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>f4fitness@naver.com</t>
+          <t>huntfitness_2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1415-7783</t>
+          <t>0507-1422-1553</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>울산 남구 삼산중로 71 3,4층</t>
+          <t>울산광역시 남구 동산로29번길 4 2-3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f4fitness</t>
+          <t>https://blog.naver.com/huntfitness_2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcc02l</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="Q3" t="n">
-        <v>495</v>
+        <v>1982</v>
       </c>
       <c r="R3" t="n">
-        <v>1589</v>
+        <v>3070</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>33706478</t>
+          <t>1960233397</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33706478</t>
+          <t>https://m.place.naver.com/place/1960233397</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디엔피트니스 PT\u002F헬스</t>
+          <t>에프포짐 헬스장&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dnfit@naver.com</t>
+          <t>f4fitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1478-3239</t>
+          <t>0507-1415-7783</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 번영로 51 3층 디엔피트니스</t>
+          <t>울산광역시 남구 삼산중로 71 3,4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dnfit_official</t>
+          <t>https://blog.naver.com/f4fitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>127</v>
+        <v>1094</v>
       </c>
       <c r="Q4" t="n">
-        <v>96</v>
+        <v>495</v>
       </c>
       <c r="R4" t="n">
-        <v>223</v>
+        <v>1589</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1215017007</t>
+          <t>33706478</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215017007</t>
+          <t>https://m.place.naver.com/place/33706478</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>울산pt핏버디짐</t>
+          <t>디엔피트니스 PT/헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fitbuddy@naver.com</t>
+          <t>dnfit@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1335-5805</t>
+          <t>0507-1478-3239</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>울산 남구 월평로 72</t>
+          <t>울산광역시 남구 번영로 51 3층 디엔피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitbuddy</t>
+          <t>https://www.instagram.com/dnfit_official</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,19 +883,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wk5k</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="Q5" t="n">
-        <v>262</v>
+        <v>96</v>
       </c>
       <c r="R5" t="n">
-        <v>362</v>
+        <v>223</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1562351903</t>
+          <t>1215017007</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1562351903</t>
+          <t>https://m.place.naver.com/place/1215017007</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>울산 PT전문 스페스짐</t>
+          <t>울산pt핏버디짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spesgym@naver.com</t>
+          <t>fitbuddy@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1441-0978</t>
+          <t>0507-1335-5805</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 남구 봉월로59번길 10 4층</t>
+          <t>울산광역시 남구 월평로 72</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spesgym</t>
+          <t>https://blog.naver.com/fitbuddy</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,19 +977,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wosoak8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1009,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="n">
-        <v>699</v>
+        <v>262</v>
       </c>
       <c r="R6" t="n">
-        <v>805</v>
+        <v>362</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1311964904</t>
+          <t>1562351903</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311964904</t>
+          <t>https://m.place.naver.com/place/1562351903</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1041,34 +1029,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT야음점</t>
+          <t>몸가짐 운동 센터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bemoveyaeum@naver.com</t>
+          <t>posture_gym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1386-7929</t>
+          <t>0507-1366-0466</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
+          <t>울산광역시 남구 번영로124번길 6 3층 몸가짐운동센터</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bemoveyaeum</t>
+          <t>https://blog.naver.com/posture_gym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1088,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40ujg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2228</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="n">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="R7" t="n">
-        <v>2736</v>
+        <v>612</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1092788853</t>
+          <t>1142634858</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092788853</t>
+          <t>https://m.place.naver.com/place/1142634858</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1144,39 +1128,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1191,7 +1175,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,17 +1185,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="R8" t="n">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산광역시 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,24 +1258,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,17 +1279,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="Q9" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="R9" t="n">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산광역시 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1382,14 +1362,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>181</v>
+        <v>1031</v>
       </c>
       <c r="Q10" t="n">
-        <v>54</v>
+        <v>459</v>
       </c>
       <c r="R10" t="n">
-        <v>235</v>
+        <v>1490</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>휘트니스클리닉 울산동구점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>fitnessclinic_ulsan1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1304-6479</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 동구 대학길 30 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,17 +1456,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1031</v>
+        <v>126</v>
       </c>
       <c r="Q11" t="n">
-        <v>459</v>
+        <v>300</v>
       </c>
       <c r="R11" t="n">
-        <v>1490</v>
+        <v>426</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,15 +1486,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>242237435</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/242237435</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>권유희운동센터</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>physiokwonyh@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1428-8122</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>울산 중구 장춘로 4 4층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/physiokwonyh</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45m5qs</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>17</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2079934760</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2079934760</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산광역시 울주군 온산읍 신경5길 36 3층</t>
+          <t>울산 울주군 온산읍 신경5길 36 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wt145ei</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>울산광역시 남구 동산로29번길 4 2-3층</t>
+          <t>울산 남구 동산로29번길 4 2-3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -769,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산광역시 남구 삼산중로 71 3,4층</t>
+          <t>울산 남구 삼산중로 71 3,4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcc02l</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -846,7 +854,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>디엔피트니스 PT/헬스</t>
+          <t>디엔피트니스 PT\u002F헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>울산광역시 남구 번영로 51 3층 디엔피트니스</t>
+          <t>울산 남구 번영로 51 3층 디엔피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -957,7 +965,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산광역시 남구 월평로 72</t>
+          <t>울산 남구 월평로 72</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +990,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wk5k</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1051,7 +1063,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산광역시 남구 번영로124번길 6 3층 몸가짐운동센터</t>
+          <t>울산 남구 번영로124번길 6 3층 몸가짐운동센터</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,34 +1135,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>온앤온피티스튜디오</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>thelastgym2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1374-9854</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 북구 동대로 142 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/on_n_on_p.t_studio?igsh=MWtxajZ4Z290cTZucQ==</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1172,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1175,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w4m9rk</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1185,17 +1197,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="Q8" t="n">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="R8" t="n">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1216,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1467612314</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1467612314</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산광역시 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1258,20 +1270,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi9p345</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,17 +1295,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="R9" t="n">
-        <v>235</v>
+        <v>168</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1336,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산광역시 중구 번영로 564 10층</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1362,10 +1378,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1031</v>
+        <v>181</v>
       </c>
       <c r="Q10" t="n">
-        <v>459</v>
+        <v>54</v>
       </c>
       <c r="R10" t="n">
-        <v>1490</v>
+        <v>235</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스클리닉 울산동구점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fitnessclinic_ulsan1@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1304-6479</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 동구 대학길 30 지하1층</t>
+          <t>울산 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1456,13 +1476,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w423pi</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1471,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>126</v>
+        <v>1031</v>
       </c>
       <c r="Q11" t="n">
-        <v>300</v>
+        <v>459</v>
       </c>
       <c r="R11" t="n">
-        <v>426</v>
+        <v>1490</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>242237435</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/242237435</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1503,34 +1527,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>권유희운동센터</t>
+          <t>휘트니스클리닉 울산동구점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>physiokwonyh@naver.com</t>
+          <t>fitnessclinic_ulsan1@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1428-8122</t>
+          <t>0507-1304-6479</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>울산 중구 장춘로 4 4층</t>
+          <t>울산 동구 대학길 30 지하1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physiokwonyh</t>
+          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1550,17 +1574,13 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45m5qs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1569,13 +1589,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="R12" t="n">
-        <v>17</v>
+        <v>426</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1584,12 +1604,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2079934760</t>
+          <t>242237435</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079934760</t>
+          <t>https://m.place.naver.com/place/242237435</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="Q2" t="n">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="R2" t="n">
-        <v>3070</v>
+        <v>3075</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -1037,39 +1037,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>온앤온피티스튜디오</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>thelastgym2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1374-9854</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 북구 동대로 142 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https://www.instagram.com/on_n_on_p.t_studio?igsh=MWtxajZ4Z290cTZucQ==</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
+          <t>https://talk.naver.com/ct/w4m9rk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="R7" t="n">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>1467612314</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/1467612314</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,29 +1140,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w40ujg</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>63</v>
+        <v>2228</v>
       </c>
       <c r="Q8" t="n">
-        <v>105</v>
+        <v>510</v>
       </c>
       <c r="R8" t="n">
-        <v>168</v>
+        <v>2738</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="R9" t="n">
-        <v>235</v>
+        <v>168</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,29 +1336,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1031</v>
+        <v>181</v>
       </c>
       <c r="Q10" t="n">
-        <v>459</v>
+        <v>54</v>
       </c>
       <c r="R10" t="n">
-        <v>1490</v>
+        <v>235</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스클리닉 울산동구점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fitnessclinic_ulsan1@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1304-6479</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 동구 대학길 30 지하1층</t>
+          <t>울산 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1476,13 +1476,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w423pi</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1491,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>126</v>
+        <v>1032</v>
       </c>
       <c r="Q11" t="n">
-        <v>300</v>
+        <v>459</v>
       </c>
       <c r="R11" t="n">
-        <v>426</v>
+        <v>1491</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>242237435</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/242237435</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="Q2" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="R2" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1140,29 +1140,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT야음점</t>
+          <t>모모짐 24헬스&amp;PT 달동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bemoveyaeum@naver.com</t>
+          <t>momogym-@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1386-7929</t>
+          <t>0507-1343-6807</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
+          <t>울산 남구 도산로 45 2층 모모짐 (MOMOGYM)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bemoveyaeum</t>
+          <t>https://www.instagram.com/momogym.xx</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ujg</t>
+          <t>https://talk.naver.com/ct/wxpbega</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2228</v>
+        <v>120</v>
       </c>
       <c r="Q8" t="n">
-        <v>510</v>
+        <v>29</v>
       </c>
       <c r="R8" t="n">
-        <v>2738</v>
+        <v>149</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1092788853</t>
+          <t>2064303253</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092788853</t>
+          <t>https://m.place.naver.com/place/2064303253</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1238,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w40ujg</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>63</v>
+        <v>2228</v>
       </c>
       <c r="Q9" t="n">
-        <v>105</v>
+        <v>510</v>
       </c>
       <c r="R9" t="n">
-        <v>168</v>
+        <v>2738</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1336,34 +1336,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,17 +1412,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1434,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1032</v>
+        <v>181</v>
       </c>
       <c r="Q11" t="n">
-        <v>459</v>
+        <v>55</v>
       </c>
       <c r="R11" t="n">
-        <v>1491</v>
+        <v>236</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="Q2" t="n">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="R2" t="n">
-        <v>3077</v>
+        <v>3081</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         <v>1094</v>
       </c>
       <c r="Q3" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="R3" t="n">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1140,29 +1140,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>모모짐 24헬스&amp;PT 달동점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>momogym-@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1343-6807</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 남구 도산로 45 2층 모모짐 (MOMOGYM)</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momogym.xx</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wxpbega</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="R8" t="n">
-        <v>149</v>
+        <v>239</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2064303253</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064303253</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT야음점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bemoveyaeum@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1386-7929</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
+          <t>울산 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bemoveyaeum</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ujg</t>
+          <t>https://talk.naver.com/ct/w423pi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2228</v>
+        <v>1033</v>
       </c>
       <c r="Q9" t="n">
-        <v>510</v>
+        <v>459</v>
       </c>
       <c r="R9" t="n">
-        <v>2738</v>
+        <v>1492</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1092788853</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092788853</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,34 +1336,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>휘트니스클리닉 울산동구점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>fitnessclinic_ulsan1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1304-6479</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 동구 대학길 30 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1373,19 +1373,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1397,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>301</v>
       </c>
       <c r="R10" t="n">
-        <v>34</v>
+        <v>427</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1408,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>242237435</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/242237435</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1429,34 +1425,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>권유희운동센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>physiokwonyh@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1428-8122</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 중구 장춘로 4 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>https://blog.naver.com/physiokwonyh</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1481,7 +1477,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/w45m5qs</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>181</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>236</v>
+        <v>17</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1506,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>2079934760</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/2079934760</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/울산_PT.xlsx
+++ b/naver-place-crawler/results_health/울산_PT.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헌트피트니스 옥동점</t>
+          <t>마디 체형교정센터</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>huntfitness_2@naver.com</t>
+          <t>madigood_@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1422-1553</t>
+          <t>0507-1337-9084</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 남구 동산로29번길 4 2-3층</t>
+          <t>울산 남구 돋질로239번길 4-11 진하우스 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huntfitness_2</t>
+          <t>https://blog.naver.com/madigood_</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45049</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1091</v>
+        <v>223</v>
       </c>
       <c r="Q2" t="n">
-        <v>1990</v>
+        <v>231</v>
       </c>
       <c r="R2" t="n">
-        <v>3081</v>
+        <v>454</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1960233397</t>
+          <t>1130601696</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1960233397</t>
+          <t>https://m.place.naver.com/place/1130601696</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에프포짐 헬스장&amp;PT 삼산점</t>
+          <t>헌트피트니스 옥동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>f4fitness@naver.com</t>
+          <t>huntfitness_2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1415-7783</t>
+          <t>0507-1422-1553</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>울산 남구 삼산중로 71 3,4층</t>
+          <t>울산 남구 동산로29번길 4 2-3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f4fitness</t>
+          <t>https://blog.naver.com/huntfitness_2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcc02l</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>496</v>
+        <v>1990</v>
       </c>
       <c r="R3" t="n">
-        <v>1590</v>
+        <v>3082</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>33706478</t>
+          <t>1960233397</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33706478</t>
+          <t>https://m.place.naver.com/place/1960233397</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디엔피트니스 PT\u002F헬스</t>
+          <t>에프포짐 헬스장&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dnfit@naver.com</t>
+          <t>f4fitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1478-3239</t>
+          <t>0507-1415-7783</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 번영로 51 3층 디엔피트니스</t>
+          <t>울산 남구 삼산중로 71 3,4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dnfit_official</t>
+          <t>https://blog.naver.com/f4fitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,15 +793,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcc02l</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>127</v>
+        <v>1094</v>
       </c>
       <c r="Q4" t="n">
-        <v>96</v>
+        <v>496</v>
       </c>
       <c r="R4" t="n">
-        <v>223</v>
+        <v>1590</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1215017007</t>
+          <t>33706478</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215017007</t>
+          <t>https://m.place.naver.com/place/33706478</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -850,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>울산pt핏버디짐</t>
+          <t>디엔피트니스 PT\u002F헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fitbuddy@naver.com</t>
+          <t>dnfit@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1335-5805</t>
+          <t>0507-1478-3239</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>울산 남구 월평로 72</t>
+          <t>울산 남구 번영로 51 3층 디엔피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitbuddy</t>
+          <t>https://www.instagram.com/dnfit_official</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,19 +891,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wk5k</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="Q5" t="n">
-        <v>262</v>
+        <v>96</v>
       </c>
       <c r="R5" t="n">
-        <v>362</v>
+        <v>223</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +926,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1562351903</t>
+          <t>1215017007</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1562351903</t>
+          <t>https://m.place.naver.com/place/1215017007</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,29 +1042,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>온앤온피티스튜디오</t>
+          <t>크로스핏모아이</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thelastgym2@naver.com</t>
+          <t>shyunjin90@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1374-9854</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 북구 동대로 142 2층</t>
+          <t>울산 남구 화합로 230</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/on_n_on_p.t_studio?igsh=MWtxajZ4Z290cTZucQ==</t>
+          <t>https://blog.naver.com/shyunjin90</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1079,19 +1075,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4m9rk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1103,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="R7" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,51 +1110,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1467612314</t>
+          <t>1291623629</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467612314</t>
+          <t>https://m.place.naver.com/place/1291623629</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>온앤온피티스튜디오</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>thelastgym2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1374-9854</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 동대로 142 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>https://www.instagram.com/on_n_on_p.t_studio?igsh=MWtxajZ4Z290cTZucQ==</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1187,7 +1179,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/w4m9rk</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="Q8" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="R8" t="n">
-        <v>239</v>
+        <v>139</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>1467612314</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/1467612314</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1238,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>모모짐 24헬스&amp;PT 달동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>momogym-@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1343-6807</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 남구 도산로 45 2층 모모짐 (MOMOGYM)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>https://www.instagram.com/momogym.xx</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,7 +1267,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1277,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
+          <t>https://talk.naver.com/ct/wxpbega</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1033</v>
+        <v>120</v>
       </c>
       <c r="Q9" t="n">
-        <v>459</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>1492</v>
+        <v>149</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>2064303253</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/2064303253</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1336,29 +1328,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스클리닉 울산동구점</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitnessclinic_ulsan1@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-6479</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 동구 대학길 30 지하1층</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1378,10 +1370,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40ujg</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1393,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>126</v>
+        <v>2231</v>
       </c>
       <c r="Q10" t="n">
-        <v>301</v>
+        <v>510</v>
       </c>
       <c r="R10" t="n">
-        <v>427</v>
+        <v>2741</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,56 +1404,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>242237435</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/242237435</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>권유희운동센터</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>physiokwonyh@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1428-8122</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 중구 장춘로 4 4층</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physiokwonyh</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1467,7 +1463,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1477,7 +1473,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45m5qs</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1491,13 +1487,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,17 +1502,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2079934760</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079934760</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
